--- a/VerveStacks_MEX_grids_kan/source_data/VerveStacks_MEX.xlsx
+++ b/VerveStacks_MEX_grids_kan/source_data/VerveStacks_MEX.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2996E903-E17C-4753-95FE-E6DAE821A4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36EAE1A1-6302-40C2-AD0F-3F7831680B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="historical_data" sheetId="4" r:id="rId1"/>
-    <sheet name="weo_pg" sheetId="50" r:id="rId2"/>
-    <sheet name="re_targets" sheetId="49" r:id="rId3"/>
-    <sheet name="ccs_retrofits" sheetId="48" r:id="rId4"/>
-    <sheet name="Calibration" sheetId="47" r:id="rId5"/>
-    <sheet name="existing_stock" sheetId="46" r:id="rId6"/>
+    <sheet name="weo_pg" sheetId="55" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="54" r:id="rId3"/>
+    <sheet name="ccs_retrofits" sheetId="53" r:id="rId4"/>
+    <sheet name="Calibration" sheetId="52" r:id="rId5"/>
+    <sheet name="existing_stock" sheetId="51" r:id="rId6"/>
     <sheet name="historical_data_long" sheetId="32" r:id="rId7"/>
     <sheet name="iamc_data" sheetId="29" r:id="rId8"/>
     <sheet name="iamc_charts" sheetId="28" r:id="rId9"/>
@@ -4481,7 +4481,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B084CFB-B94E-D558-2A2C-AC3ACAB6DB85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7660C0C-C79B-4279-FE70-8FEBEA8F0EF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4536,7 +4536,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DD5976A-B2AC-33BD-28DE-D4A72359F8AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811E3E84-E3EC-E58E-AEE6-131C400A1BB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12356,7 +12356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B766769-1AEC-4114-98D3-9B731368323A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F810A676-C0DD-4370-9AC1-730DB6901427}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15484,7 +15484,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E814B4-7609-4240-B7C0-0F6C555FBB46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{361A7947-F444-4D6E-8DB0-C76ADDCEB9D9}">
   <dimension ref="B2:L33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16584,7 +16584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5063F1E6-5A97-40EF-B474-5EA366CBD617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4561FB-D4A0-4612-A76F-9F85326E411D}">
   <dimension ref="B2:J170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16639,13 +16639,13 @@
         <v>4.59</v>
       </c>
       <c r="G4">
-        <v>7.350656160000002E-2</v>
+        <v>6.1423291200000014E-2</v>
       </c>
       <c r="H4">
         <v>0.5605</v>
       </c>
       <c r="I4">
-        <v>0.24179790000000001</v>
+        <v>0.20205030000000002</v>
       </c>
       <c r="J4" t="s">
         <v>699</v>
@@ -16668,13 +16668,13 @@
         <v>4.59</v>
       </c>
       <c r="G5">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="H5">
         <v>0.5605</v>
       </c>
       <c r="I5">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J5" t="s">
         <v>75</v>
@@ -16697,13 +16697,13 @@
         <v>4.59</v>
       </c>
       <c r="G6">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="H6">
         <v>0.5605</v>
       </c>
       <c r="I6">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J6" t="s">
         <v>79</v>
@@ -16726,13 +16726,13 @@
         <v>4.59</v>
       </c>
       <c r="G7">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="H7">
         <v>0.5605</v>
       </c>
       <c r="I7">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J7" t="s">
         <v>80</v>
@@ -16755,13 +16755,13 @@
         <v>4.59</v>
       </c>
       <c r="G8">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="H8">
         <v>0.5605</v>
       </c>
       <c r="I8">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J8" t="s">
         <v>81</v>
@@ -16784,13 +16784,13 @@
         <v>4.59</v>
       </c>
       <c r="G9">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H9">
         <v>0.5605</v>
       </c>
       <c r="I9">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J9" t="s">
         <v>82</v>
@@ -16813,13 +16813,13 @@
         <v>4.59</v>
       </c>
       <c r="G10">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H10">
         <v>0.5605</v>
       </c>
       <c r="I10">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J10" t="s">
         <v>83</v>
@@ -16842,13 +16842,13 @@
         <v>4.59</v>
       </c>
       <c r="G11">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H11">
         <v>0.5605</v>
       </c>
       <c r="I11">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J11" t="s">
         <v>84</v>
@@ -16871,13 +16871,13 @@
         <v>4.59</v>
       </c>
       <c r="G12">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H12">
         <v>0.5605</v>
       </c>
       <c r="I12">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J12" t="s">
         <v>85</v>
@@ -16900,13 +16900,13 @@
         <v>4.59</v>
       </c>
       <c r="G13">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H13">
         <v>0.5605</v>
       </c>
       <c r="I13">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J13" t="s">
         <v>86</v>
@@ -16929,13 +16929,13 @@
         <v>4.59</v>
       </c>
       <c r="G14">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H14">
         <v>0.5605</v>
       </c>
       <c r="I14">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J14" t="s">
         <v>89</v>
@@ -16958,13 +16958,13 @@
         <v>4.59</v>
       </c>
       <c r="G15">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H15">
         <v>0.5605</v>
       </c>
       <c r="I15">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J15" t="s">
         <v>90</v>
@@ -16987,13 +16987,13 @@
         <v>4.59</v>
       </c>
       <c r="G16">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H16">
         <v>0.5605</v>
       </c>
       <c r="I16">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J16" t="s">
         <v>91</v>
@@ -17016,13 +17016,13 @@
         <v>4.59</v>
       </c>
       <c r="G17">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H17">
         <v>0.5605</v>
       </c>
       <c r="I17">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J17" t="s">
         <v>92</v>
@@ -17045,13 +17045,13 @@
         <v>4.59</v>
       </c>
       <c r="G18">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="H18">
         <v>0.5605</v>
       </c>
       <c r="I18">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J18" t="s">
         <v>93</v>
@@ -17074,13 +17074,13 @@
         <v>3.52</v>
       </c>
       <c r="G19">
-        <v>0.20011490000000001</v>
+        <v>0.16721930000000002</v>
       </c>
       <c r="H19">
         <v>0.72770000000000001</v>
       </c>
       <c r="I19">
-        <v>0.28835</v>
+        <v>0.24095</v>
       </c>
       <c r="J19" t="s">
         <v>94</v>
@@ -17103,13 +17103,13 @@
         <v>3.75</v>
       </c>
       <c r="G20">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H20">
         <v>0.84455000000000002</v>
       </c>
       <c r="I20">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J20" t="s">
         <v>96</v>
@@ -17132,13 +17132,13 @@
         <v>3.75</v>
       </c>
       <c r="G21">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H21">
         <v>0.84455000000000002</v>
       </c>
       <c r="I21">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J21" t="s">
         <v>99</v>
@@ -17161,13 +17161,13 @@
         <v>3.75</v>
       </c>
       <c r="G22">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H22">
         <v>0.84455000000000002</v>
       </c>
       <c r="I22">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J22" t="s">
         <v>102</v>
@@ -17190,13 +17190,13 @@
         <v>3.75</v>
       </c>
       <c r="G23">
-        <v>0.370475</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H23">
         <v>0.84455000000000002</v>
       </c>
       <c r="I23">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J23" t="s">
         <v>103</v>
@@ -17219,13 +17219,13 @@
         <v>3.75</v>
       </c>
       <c r="G24">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H24">
         <v>0.84455000000000002</v>
       </c>
       <c r="I24">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J24" t="s">
         <v>106</v>
@@ -17248,13 +17248,13 @@
         <v>3.75</v>
       </c>
       <c r="G25">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H25">
         <v>0.84455000000000002</v>
       </c>
       <c r="I25">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J25" t="s">
         <v>109</v>
@@ -17277,13 +17277,13 @@
         <v>3.75</v>
       </c>
       <c r="G26">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="H26">
         <v>0.84455000000000002</v>
       </c>
       <c r="I26">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="J26" t="s">
         <v>112</v>
@@ -17306,13 +17306,13 @@
         <v>3.75</v>
       </c>
       <c r="G27">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999992</v>
       </c>
       <c r="H27">
         <v>0.84455000000000002</v>
       </c>
       <c r="I27">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="J27" t="s">
         <v>114</v>
@@ -17335,13 +17335,13 @@
         <v>3.75</v>
       </c>
       <c r="G28">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H28">
         <v>0.84455000000000002</v>
       </c>
       <c r="I28">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J28" t="s">
         <v>117</v>
@@ -17364,13 +17364,13 @@
         <v>3.75</v>
       </c>
       <c r="G29">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="H29">
         <v>0.84455000000000002</v>
       </c>
       <c r="I29">
-        <v>0.42339999999999989</v>
+        <v>0.3538</v>
       </c>
       <c r="J29" t="s">
         <v>119</v>
@@ -17393,13 +17393,13 @@
         <v>3.75</v>
       </c>
       <c r="G30">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H30">
         <v>0.84455000000000002</v>
       </c>
       <c r="I30">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J30" t="s">
         <v>122</v>
@@ -17422,13 +17422,13 @@
         <v>3.75</v>
       </c>
       <c r="G31">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H31">
         <v>0.84455000000000002</v>
       </c>
       <c r="I31">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J31" t="s">
         <v>125</v>
@@ -17451,13 +17451,13 @@
         <v>3.75</v>
       </c>
       <c r="G32">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H32">
         <v>0.84455000000000002</v>
       </c>
       <c r="I32">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J32" t="s">
         <v>126</v>
@@ -17480,13 +17480,13 @@
         <v>3.75</v>
       </c>
       <c r="G33">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H33">
         <v>0.84455000000000002</v>
       </c>
       <c r="I33">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J33" t="s">
         <v>128</v>
@@ -17509,13 +17509,13 @@
         <v>3.75</v>
       </c>
       <c r="G34">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H34">
         <v>0.84455000000000002</v>
       </c>
       <c r="I34">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J34" t="s">
         <v>131</v>
@@ -17538,13 +17538,13 @@
         <v>3.75</v>
       </c>
       <c r="G35">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H35">
         <v>0.84455000000000002</v>
       </c>
       <c r="I35">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J35" t="s">
         <v>133</v>
@@ -17567,13 +17567,13 @@
         <v>3.75</v>
       </c>
       <c r="G36">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H36">
         <v>0.84455000000000002</v>
       </c>
       <c r="I36">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J36" t="s">
         <v>134</v>
@@ -17596,13 +17596,13 @@
         <v>3.75</v>
       </c>
       <c r="G37">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H37">
         <v>0.84455000000000002</v>
       </c>
       <c r="I37">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J37" t="s">
         <v>137</v>
@@ -17625,13 +17625,13 @@
         <v>3.75</v>
       </c>
       <c r="G38">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H38">
         <v>0.84455000000000002</v>
       </c>
       <c r="I38">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J38" t="s">
         <v>138</v>
@@ -17654,13 +17654,13 @@
         <v>3.75</v>
       </c>
       <c r="G39">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H39">
         <v>0.84455000000000002</v>
       </c>
       <c r="I39">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J39" t="s">
         <v>141</v>
@@ -17683,13 +17683,13 @@
         <v>3.75</v>
       </c>
       <c r="G40">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="H40">
         <v>0.84455000000000002</v>
       </c>
       <c r="I40">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="J40" t="s">
         <v>142</v>
@@ -17712,13 +17712,13 @@
         <v>3.75</v>
       </c>
       <c r="G41">
-        <v>0.28743750000000001</v>
+        <v>0.2401875</v>
       </c>
       <c r="H41">
         <v>0.84455000000000002</v>
       </c>
       <c r="I41">
-        <v>0.32850000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="J41" t="s">
         <v>144</v>
@@ -17741,13 +17741,13 @@
         <v>3.75</v>
       </c>
       <c r="G42">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H42">
         <v>0.84455000000000002</v>
       </c>
       <c r="I42">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J42" t="s">
         <v>146</v>
@@ -17770,13 +17770,13 @@
         <v>3.75</v>
       </c>
       <c r="G43">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H43">
         <v>0.84455000000000002</v>
       </c>
       <c r="I43">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J43" t="s">
         <v>148</v>
@@ -17799,13 +17799,13 @@
         <v>3.75</v>
       </c>
       <c r="G44">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999988</v>
       </c>
       <c r="H44">
         <v>0.84455000000000002</v>
       </c>
       <c r="I44">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999989</v>
       </c>
       <c r="J44" t="s">
         <v>149</v>
@@ -17828,13 +17828,13 @@
         <v>3.75</v>
       </c>
       <c r="G45">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="H45">
         <v>0.84455000000000002</v>
       </c>
       <c r="I45">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="J45" t="s">
         <v>151</v>
@@ -17857,13 +17857,13 @@
         <v>3.75</v>
       </c>
       <c r="G46">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H46">
         <v>0.84455000000000002</v>
       </c>
       <c r="I46">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J46" t="s">
         <v>152</v>
@@ -17886,13 +17886,13 @@
         <v>3.75</v>
       </c>
       <c r="G47">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H47">
         <v>0.84455000000000002</v>
       </c>
       <c r="I47">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J47" t="s">
         <v>156</v>
@@ -17915,13 +17915,13 @@
         <v>3.75</v>
       </c>
       <c r="G48">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H48">
         <v>0.84455000000000002</v>
       </c>
       <c r="I48">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J48" t="s">
         <v>157</v>
@@ -17944,13 +17944,13 @@
         <v>3.75</v>
       </c>
       <c r="G49">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H49">
         <v>0.84455000000000002</v>
       </c>
       <c r="I49">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J49" t="s">
         <v>159</v>
@@ -17973,13 +17973,13 @@
         <v>3.75</v>
       </c>
       <c r="G50">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999992</v>
       </c>
       <c r="H50">
         <v>0.84455000000000002</v>
       </c>
       <c r="I50">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="J50" t="s">
         <v>161</v>
@@ -18002,13 +18002,13 @@
         <v>3.75</v>
       </c>
       <c r="G51">
-        <v>0.38325000000000004</v>
+        <v>0.32025000000000003</v>
       </c>
       <c r="H51">
         <v>0.84455000000000002</v>
       </c>
       <c r="I51">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="J51" t="s">
         <v>163</v>
@@ -18031,13 +18031,13 @@
         <v>3.75</v>
       </c>
       <c r="G52">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H52">
         <v>0.84455000000000002</v>
       </c>
       <c r="I52">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J52" t="s">
         <v>165</v>
@@ -18060,13 +18060,13 @@
         <v>3.75</v>
       </c>
       <c r="G53">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H53">
         <v>0.84455000000000002</v>
       </c>
       <c r="I53">
-        <v>0.39784999999999998</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J53" t="s">
         <v>166</v>
@@ -18089,13 +18089,13 @@
         <v>3.75</v>
       </c>
       <c r="G54">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H54">
         <v>0.84455000000000002</v>
       </c>
       <c r="I54">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J54" t="s">
         <v>169</v>
@@ -18118,13 +18118,13 @@
         <v>3.75</v>
       </c>
       <c r="G55">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H55">
         <v>0.84455000000000002</v>
       </c>
       <c r="I55">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J55" t="s">
         <v>171</v>
@@ -18147,13 +18147,13 @@
         <v>3.75</v>
       </c>
       <c r="G56">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H56">
         <v>0.84455000000000002</v>
       </c>
       <c r="I56">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J56" t="s">
         <v>173</v>
@@ -18176,13 +18176,13 @@
         <v>3.75</v>
       </c>
       <c r="G57">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H57">
         <v>0.84455000000000002</v>
       </c>
       <c r="I57">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J57" t="s">
         <v>176</v>
@@ -18205,13 +18205,13 @@
         <v>3.75</v>
       </c>
       <c r="G58">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H58">
         <v>0.84455000000000002</v>
       </c>
       <c r="I58">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J58" t="s">
         <v>177</v>
@@ -18234,13 +18234,13 @@
         <v>3.75</v>
       </c>
       <c r="G59">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H59">
         <v>0.84455000000000002</v>
       </c>
       <c r="I59">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J59" t="s">
         <v>179</v>
@@ -18263,13 +18263,13 @@
         <v>3.75</v>
       </c>
       <c r="G60">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H60">
         <v>0.84455000000000002</v>
       </c>
       <c r="I60">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J60" t="s">
         <v>180</v>
@@ -18292,13 +18292,13 @@
         <v>3.75</v>
       </c>
       <c r="G61">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H61">
         <v>0.84455000000000002</v>
       </c>
       <c r="I61">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J61" t="s">
         <v>181</v>
@@ -18321,13 +18321,13 @@
         <v>3.75</v>
       </c>
       <c r="G62">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H62">
         <v>0.84455000000000002</v>
       </c>
       <c r="I62">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J62" t="s">
         <v>182</v>
@@ -18350,13 +18350,13 @@
         <v>3.75</v>
       </c>
       <c r="G63">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H63">
         <v>0.84455000000000002</v>
       </c>
       <c r="I63">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J63" t="s">
         <v>183</v>
@@ -18379,13 +18379,13 @@
         <v>3.75</v>
       </c>
       <c r="G64">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="H64">
         <v>0.84455000000000002</v>
       </c>
       <c r="I64">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="J64" t="s">
         <v>185</v>
@@ -18408,13 +18408,13 @@
         <v>3.75</v>
       </c>
       <c r="G65">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H65">
         <v>0.84455000000000002</v>
       </c>
       <c r="I65">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J65" t="s">
         <v>188</v>
@@ -18437,13 +18437,13 @@
         <v>3.75</v>
       </c>
       <c r="G66">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H66">
         <v>0.84455000000000002</v>
       </c>
       <c r="I66">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J66" t="s">
         <v>189</v>
@@ -18466,13 +18466,13 @@
         <v>3.75</v>
       </c>
       <c r="G67">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="H67">
         <v>0.84455000000000002</v>
       </c>
       <c r="I67">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="J67" t="s">
         <v>193</v>
@@ -18495,13 +18495,13 @@
         <v>3.75</v>
       </c>
       <c r="G68">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H68">
         <v>0.84455000000000002</v>
       </c>
       <c r="I68">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J68" t="s">
         <v>195</v>
@@ -18524,13 +18524,13 @@
         <v>3.75</v>
       </c>
       <c r="G69">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H69">
         <v>0.84455000000000002</v>
       </c>
       <c r="I69">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J69" t="s">
         <v>197</v>
@@ -18553,13 +18553,13 @@
         <v>3.75</v>
       </c>
       <c r="G70">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H70">
         <v>0.84455000000000002</v>
       </c>
       <c r="I70">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J70" t="s">
         <v>198</v>
@@ -18582,13 +18582,13 @@
         <v>3.75</v>
       </c>
       <c r="G71">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H71">
         <v>0.84455000000000002</v>
       </c>
       <c r="I71">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J71" t="s">
         <v>199</v>
@@ -18611,13 +18611,13 @@
         <v>3.75</v>
       </c>
       <c r="G72">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H72">
         <v>0.84455000000000002</v>
       </c>
       <c r="I72">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J72" t="s">
         <v>201</v>
@@ -18640,13 +18640,13 @@
         <v>3.75</v>
       </c>
       <c r="G73">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H73">
         <v>0.84455000000000002</v>
       </c>
       <c r="I73">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J73" t="s">
         <v>202</v>
@@ -18669,13 +18669,13 @@
         <v>3.75</v>
       </c>
       <c r="G74">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H74">
         <v>0.84455000000000002</v>
       </c>
       <c r="I74">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J74" t="s">
         <v>203</v>
@@ -18698,13 +18698,13 @@
         <v>3.75</v>
       </c>
       <c r="G75">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H75">
         <v>0.84455000000000002</v>
       </c>
       <c r="I75">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J75" t="s">
         <v>205</v>
@@ -18727,13 +18727,13 @@
         <v>3.75</v>
       </c>
       <c r="G76">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H76">
         <v>0.84455000000000002</v>
       </c>
       <c r="I76">
-        <v>0.43799999999999994</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J76" t="s">
         <v>206</v>
@@ -18756,13 +18756,13 @@
         <v>3.75</v>
       </c>
       <c r="G77">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H77">
         <v>0.84455000000000002</v>
       </c>
       <c r="I77">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J77" t="s">
         <v>209</v>
@@ -18785,13 +18785,13 @@
         <v>3.75</v>
       </c>
       <c r="G78">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H78">
         <v>0.84455000000000002</v>
       </c>
       <c r="I78">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J78" t="s">
         <v>211</v>
@@ -18814,13 +18814,13 @@
         <v>3.75</v>
       </c>
       <c r="G79">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H79">
         <v>0.84455000000000002</v>
       </c>
       <c r="I79">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J79" t="s">
         <v>212</v>
@@ -18843,13 +18843,13 @@
         <v>3.75</v>
       </c>
       <c r="G80">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H80">
         <v>0.84455000000000002</v>
       </c>
       <c r="I80">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J80" t="s">
         <v>213</v>
@@ -18872,13 +18872,13 @@
         <v>3.75</v>
       </c>
       <c r="G81">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H81">
         <v>0.84455000000000002</v>
       </c>
       <c r="I81">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J81" t="s">
         <v>214</v>
@@ -18901,13 +18901,13 @@
         <v>3.75</v>
       </c>
       <c r="G82">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H82">
         <v>0.84455000000000002</v>
       </c>
       <c r="I82">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J82" t="s">
         <v>215</v>
@@ -18930,13 +18930,13 @@
         <v>3.75</v>
       </c>
       <c r="G83">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H83">
         <v>0.84455000000000002</v>
       </c>
       <c r="I83">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J83" t="s">
         <v>216</v>
@@ -18959,13 +18959,13 @@
         <v>3.75</v>
       </c>
       <c r="G84">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H84">
         <v>0.84455000000000002</v>
       </c>
       <c r="I84">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J84" t="s">
         <v>217</v>
@@ -18988,13 +18988,13 @@
         <v>3.75</v>
       </c>
       <c r="G85">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H85">
         <v>0.84455000000000002</v>
       </c>
       <c r="I85">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J85" t="s">
         <v>218</v>
@@ -19017,13 +19017,13 @@
         <v>3.75</v>
       </c>
       <c r="G86">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H86">
         <v>0.84455000000000002</v>
       </c>
       <c r="I86">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J86" t="s">
         <v>219</v>
@@ -19046,13 +19046,13 @@
         <v>3.75</v>
       </c>
       <c r="G87">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H87">
         <v>0.84455000000000002</v>
       </c>
       <c r="I87">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J87" t="s">
         <v>220</v>
@@ -19075,13 +19075,13 @@
         <v>3.75</v>
       </c>
       <c r="G88">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H88">
         <v>0.84455000000000002</v>
       </c>
       <c r="I88">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J88" t="s">
         <v>221</v>
@@ -19104,13 +19104,13 @@
         <v>3.75</v>
       </c>
       <c r="G89">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H89">
         <v>0.84455000000000002</v>
       </c>
       <c r="I89">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J89" t="s">
         <v>222</v>
@@ -19133,13 +19133,13 @@
         <v>3.75</v>
       </c>
       <c r="G90">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="H90">
         <v>0.84455000000000002</v>
       </c>
       <c r="I90">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="J90" t="s">
         <v>223</v>
@@ -19162,13 +19162,13 @@
         <v>3.75</v>
       </c>
       <c r="G91">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H91">
         <v>0.84455000000000002</v>
       </c>
       <c r="I91">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J91" t="s">
         <v>224</v>
@@ -19191,13 +19191,13 @@
         <v>3.75</v>
       </c>
       <c r="G92">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H92">
         <v>0.84455000000000002</v>
       </c>
       <c r="I92">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J92" t="s">
         <v>225</v>
@@ -19220,13 +19220,13 @@
         <v>3.75</v>
       </c>
       <c r="G93">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H93">
         <v>0.84455000000000002</v>
       </c>
       <c r="I93">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J93" t="s">
         <v>228</v>
@@ -19249,13 +19249,13 @@
         <v>3.75</v>
       </c>
       <c r="G94">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H94">
         <v>0.84455000000000002</v>
       </c>
       <c r="I94">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J94" t="s">
         <v>229</v>
@@ -19278,13 +19278,13 @@
         <v>3.75</v>
       </c>
       <c r="G95">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H95">
         <v>0.84455000000000002</v>
       </c>
       <c r="I95">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J95" t="s">
         <v>231</v>
@@ -19307,13 +19307,13 @@
         <v>3.75</v>
       </c>
       <c r="G96">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H96">
         <v>0.84455000000000002</v>
       </c>
       <c r="I96">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J96" t="s">
         <v>232</v>
@@ -19336,13 +19336,13 @@
         <v>3.75</v>
       </c>
       <c r="G97">
-        <v>0.38325000000000004</v>
+        <v>0.32025000000000003</v>
       </c>
       <c r="H97">
         <v>0.84455000000000002</v>
       </c>
       <c r="I97">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="J97" t="s">
         <v>233</v>
@@ -19365,13 +19365,13 @@
         <v>3.75</v>
       </c>
       <c r="G98">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="H98">
         <v>0.84455000000000002</v>
       </c>
       <c r="I98">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="J98" t="s">
         <v>234</v>
@@ -19394,13 +19394,13 @@
         <v>3.75</v>
       </c>
       <c r="G99">
-        <v>0.370475</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H99">
         <v>0.84455000000000002</v>
       </c>
       <c r="I99">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J99" t="s">
         <v>236</v>
@@ -19423,13 +19423,13 @@
         <v>3.75</v>
       </c>
       <c r="G100">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="H100">
         <v>0.84455000000000002</v>
       </c>
       <c r="I100">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J100" t="s">
         <v>1228</v>
@@ -19452,13 +19452,13 @@
         <v>3.75</v>
       </c>
       <c r="G101">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H101">
         <v>0.84455000000000002</v>
       </c>
       <c r="I101">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J101" t="s">
         <v>1229</v>
@@ -19481,13 +19481,13 @@
         <v>3.75</v>
       </c>
       <c r="G102">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H102">
         <v>0.84455000000000002</v>
       </c>
       <c r="I102">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J102" t="s">
         <v>1230</v>
@@ -19510,13 +19510,13 @@
         <v>3.75</v>
       </c>
       <c r="G103">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H103">
         <v>0.84455000000000002</v>
       </c>
       <c r="I103">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J103" t="s">
         <v>1233</v>
@@ -19539,13 +19539,13 @@
         <v>3.75</v>
       </c>
       <c r="G104">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H104">
         <v>0.84455000000000002</v>
       </c>
       <c r="I104">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J104" t="s">
         <v>1236</v>
@@ -19568,13 +19568,13 @@
         <v>3.75</v>
       </c>
       <c r="G105">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="H105">
         <v>0.84455000000000002</v>
       </c>
       <c r="I105">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J105" t="s">
         <v>1239</v>
@@ -19597,13 +19597,13 @@
         <v>3.75</v>
       </c>
       <c r="G106">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H106">
         <v>0.84455000000000002</v>
       </c>
       <c r="I106">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J106" t="s">
         <v>1242</v>
@@ -19626,13 +19626,13 @@
         <v>3.75</v>
       </c>
       <c r="G107">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="H107">
         <v>0.84455000000000002</v>
       </c>
       <c r="I107">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="J107" t="s">
         <v>1243</v>
@@ -19655,13 +19655,13 @@
         <v>3.75</v>
       </c>
       <c r="G108">
-        <v>0.24272499999999997</v>
+        <v>0.20282499999999998</v>
       </c>
       <c r="H108">
         <v>0.84455000000000002</v>
       </c>
       <c r="I108">
-        <v>0.27739999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="J108" t="s">
         <v>1244</v>
@@ -19684,13 +19684,13 @@
         <v>3.75</v>
       </c>
       <c r="G109">
-        <v>0.35770000000000002</v>
+        <v>0.29890000000000005</v>
       </c>
       <c r="H109">
         <v>0.84455000000000002</v>
       </c>
       <c r="I109">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000007</v>
       </c>
       <c r="J109" t="s">
         <v>1245</v>
@@ -19713,13 +19713,13 @@
         <v>3.75</v>
       </c>
       <c r="G110">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="H110">
         <v>0.84455000000000002</v>
       </c>
       <c r="I110">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J110" t="s">
         <v>1248</v>
@@ -19742,13 +19742,13 @@
         <v>3.75</v>
       </c>
       <c r="G111">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="H111">
         <v>0.84455000000000002</v>
       </c>
       <c r="I111">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="J111" t="s">
         <v>1249</v>
@@ -19771,13 +19771,13 @@
         <v>3.75</v>
       </c>
       <c r="G112">
-        <v>0.33215000000000006</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="H112">
         <v>0.84455000000000002</v>
       </c>
       <c r="I112">
-        <v>0.37960000000000005</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="J112" t="s">
         <v>1250</v>
@@ -19800,13 +19800,13 @@
         <v>3.75</v>
       </c>
       <c r="G113">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="H113">
         <v>0.84455000000000002</v>
       </c>
       <c r="I113">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J113" t="s">
         <v>1253</v>
@@ -19829,13 +19829,13 @@
         <v>3.75</v>
       </c>
       <c r="G114">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H114">
         <v>0.84455000000000002</v>
       </c>
       <c r="I114">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J114" t="s">
         <v>237</v>
@@ -19858,13 +19858,13 @@
         <v>3.75</v>
       </c>
       <c r="G115">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H115">
         <v>0.84455000000000002</v>
       </c>
       <c r="I115">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J115" t="s">
         <v>239</v>
@@ -19887,13 +19887,13 @@
         <v>3.75</v>
       </c>
       <c r="G116">
-        <v>0.16288125000000001</v>
+        <v>0.13610624999999998</v>
       </c>
       <c r="H116">
         <v>0.84455000000000002</v>
       </c>
       <c r="I116">
-        <v>0.18615000000000001</v>
+        <v>0.15554999999999999</v>
       </c>
       <c r="J116" t="s">
         <v>1256</v>
@@ -19916,13 +19916,13 @@
         <v>3.75</v>
       </c>
       <c r="G117">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H117">
         <v>0.84455000000000002</v>
       </c>
       <c r="I117">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J117" t="s">
         <v>1259</v>
@@ -19945,13 +19945,13 @@
         <v>3.75</v>
       </c>
       <c r="G118">
-        <v>0.16926875000000002</v>
+        <v>0.14144375000000001</v>
       </c>
       <c r="H118">
         <v>0.84455000000000002</v>
       </c>
       <c r="I118">
-        <v>0.19345000000000001</v>
+        <v>0.16165000000000002</v>
       </c>
       <c r="J118" t="s">
         <v>1260</v>
@@ -19974,13 +19974,13 @@
         <v>3.75</v>
       </c>
       <c r="G119">
-        <v>0.18523749999999997</v>
+        <v>0.15478749999999997</v>
       </c>
       <c r="H119">
         <v>0.84455000000000002</v>
       </c>
       <c r="I119">
-        <v>0.21169999999999997</v>
+        <v>0.17689999999999997</v>
       </c>
       <c r="J119" t="s">
         <v>1261</v>
@@ -20003,13 +20003,13 @@
         <v>3.75</v>
       </c>
       <c r="G120">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H120">
         <v>0.84455000000000002</v>
       </c>
       <c r="I120">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J120" t="s">
         <v>1262</v>
@@ -20032,13 +20032,13 @@
         <v>3.75</v>
       </c>
       <c r="G121">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H121">
         <v>0.84455000000000002</v>
       </c>
       <c r="I121">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J121" t="s">
         <v>1263</v>
@@ -20061,13 +20061,13 @@
         <v>3.75</v>
       </c>
       <c r="G122">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H122">
         <v>0.84455000000000002</v>
       </c>
       <c r="I122">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J122" t="s">
         <v>1264</v>
@@ -20090,13 +20090,13 @@
         <v>3.75</v>
       </c>
       <c r="G123">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="H123">
         <v>0.84455000000000002</v>
       </c>
       <c r="I123">
-        <v>0.26279999999999998</v>
+        <v>0.21960000000000002</v>
       </c>
       <c r="J123" t="s">
         <v>240</v>
@@ -20119,13 +20119,13 @@
         <v>3.75</v>
       </c>
       <c r="G124">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="H124">
         <v>0.84455000000000002</v>
       </c>
       <c r="I124">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J124" t="s">
         <v>242</v>
@@ -20148,13 +20148,13 @@
         <v>3.75</v>
       </c>
       <c r="G125">
-        <v>0.22675624999999999</v>
+        <v>0.18948125000000002</v>
       </c>
       <c r="H125">
         <v>0.84455000000000002</v>
       </c>
       <c r="I125">
-        <v>0.25914999999999999</v>
+        <v>0.21654999999999999</v>
       </c>
       <c r="J125" t="s">
         <v>1267</v>
@@ -20177,13 +20177,13 @@
         <v>3.75</v>
       </c>
       <c r="G126">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="H126">
         <v>0.84455000000000002</v>
       </c>
       <c r="I126">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J126" t="s">
         <v>1268</v>
@@ -20206,13 +20206,13 @@
         <v>3.75</v>
       </c>
       <c r="G127">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="H127">
         <v>0.84455000000000002</v>
       </c>
       <c r="I127">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="J127" t="s">
         <v>1271</v>
@@ -20235,13 +20235,13 @@
         <v>3.75</v>
       </c>
       <c r="G128">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H128">
         <v>0.84455000000000002</v>
       </c>
       <c r="I128">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J128" t="s">
         <v>243</v>
@@ -20264,13 +20264,13 @@
         <v>3.75</v>
       </c>
       <c r="G129">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H129">
         <v>0.84455000000000002</v>
       </c>
       <c r="I129">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J129" t="s">
         <v>245</v>
@@ -20293,13 +20293,13 @@
         <v>3.75</v>
       </c>
       <c r="G130">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H130">
         <v>0.84455000000000002</v>
       </c>
       <c r="I130">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J130" t="s">
         <v>246</v>
@@ -20322,13 +20322,13 @@
         <v>3.75</v>
       </c>
       <c r="G131">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H131">
         <v>0.84455000000000002</v>
       </c>
       <c r="I131">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J131" t="s">
         <v>247</v>
@@ -20351,13 +20351,13 @@
         <v>3.75</v>
       </c>
       <c r="G132">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H132">
         <v>0.84455000000000002</v>
       </c>
       <c r="I132">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J132" t="s">
         <v>248</v>
@@ -20380,13 +20380,13 @@
         <v>3.75</v>
       </c>
       <c r="G133">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H133">
         <v>0.84455000000000002</v>
       </c>
       <c r="I133">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J133" t="s">
         <v>250</v>
@@ -20409,13 +20409,13 @@
         <v>3.75</v>
       </c>
       <c r="G134">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H134">
         <v>0.84455000000000002</v>
       </c>
       <c r="I134">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J134" t="s">
         <v>251</v>
@@ -20438,13 +20438,13 @@
         <v>3.75</v>
       </c>
       <c r="G135">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H135">
         <v>0.84455000000000002</v>
       </c>
       <c r="I135">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J135" t="s">
         <v>252</v>
@@ -20467,13 +20467,13 @@
         <v>3.75</v>
       </c>
       <c r="G136">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H136">
         <v>0.84455000000000002</v>
       </c>
       <c r="I136">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J136" t="s">
         <v>253</v>
@@ -20496,13 +20496,13 @@
         <v>3.75</v>
       </c>
       <c r="G137">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H137">
         <v>0.84455000000000002</v>
       </c>
       <c r="I137">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J137" t="s">
         <v>254</v>
@@ -20525,13 +20525,13 @@
         <v>3.75</v>
       </c>
       <c r="G138">
-        <v>0.21717500000000001</v>
+        <v>0.18147499999999997</v>
       </c>
       <c r="H138">
         <v>0.84455000000000002</v>
       </c>
       <c r="I138">
-        <v>0.2482</v>
+        <v>0.20739999999999997</v>
       </c>
       <c r="J138" t="s">
         <v>1274</v>
@@ -20554,13 +20554,13 @@
         <v>3.75</v>
       </c>
       <c r="G139">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H139">
         <v>0.84455000000000002</v>
       </c>
       <c r="I139">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J139" t="s">
         <v>1277</v>
@@ -20583,13 +20583,13 @@
         <v>3.75</v>
       </c>
       <c r="G140">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H140">
         <v>0.84455000000000002</v>
       </c>
       <c r="I140">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J140" t="s">
         <v>1278</v>
@@ -20612,13 +20612,13 @@
         <v>3.75</v>
       </c>
       <c r="G141">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H141">
         <v>0.84455000000000002</v>
       </c>
       <c r="I141">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J141" t="s">
         <v>1279</v>
@@ -20641,13 +20641,13 @@
         <v>3.75</v>
       </c>
       <c r="G142">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H142">
         <v>0.84455000000000002</v>
       </c>
       <c r="I142">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J142" t="s">
         <v>1280</v>
@@ -20670,13 +20670,13 @@
         <v>3.75</v>
       </c>
       <c r="G143">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H143">
         <v>0.84455000000000002</v>
       </c>
       <c r="I143">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J143" t="s">
         <v>1281</v>
@@ -20699,13 +20699,13 @@
         <v>3.75</v>
       </c>
       <c r="G144">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="H144">
         <v>0.84455000000000002</v>
       </c>
       <c r="I144">
-        <v>0.24089999999999998</v>
+        <v>0.20129999999999998</v>
       </c>
       <c r="J144" t="s">
         <v>1284</v>
@@ -20728,13 +20728,13 @@
         <v>3.75</v>
       </c>
       <c r="G145">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H145">
         <v>0.84455000000000002</v>
       </c>
       <c r="I145">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J145" t="s">
         <v>1285</v>
@@ -20757,13 +20757,13 @@
         <v>3.75</v>
       </c>
       <c r="G146">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H146">
         <v>0.84455000000000002</v>
       </c>
       <c r="I146">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J146" t="s">
         <v>1286</v>
@@ -20786,13 +20786,13 @@
         <v>3.75</v>
       </c>
       <c r="G147">
-        <v>0.21717499999999998</v>
+        <v>0.181475</v>
       </c>
       <c r="H147">
         <v>0.84455000000000002</v>
       </c>
       <c r="I147">
-        <v>0.24819999999999998</v>
+        <v>0.2074</v>
       </c>
       <c r="J147" t="s">
         <v>1289</v>
@@ -20815,13 +20815,13 @@
         <v>3.75</v>
       </c>
       <c r="G148">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H148">
         <v>0.84455000000000002</v>
       </c>
       <c r="I148">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J148" t="s">
         <v>1290</v>
@@ -20960,13 +20960,13 @@
         <v>3.75</v>
       </c>
       <c r="G153">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="H153">
         <v>0.84455000000000002</v>
       </c>
       <c r="I153">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="J153" t="s">
         <v>304</v>
@@ -20989,13 +20989,13 @@
         <v>3.75</v>
       </c>
       <c r="G154">
-        <v>0.15329999999999999</v>
+        <v>0.12809999999999999</v>
       </c>
       <c r="H154">
         <v>0.84455000000000002</v>
       </c>
       <c r="I154">
-        <v>0.17519999999999999</v>
+        <v>0.1464</v>
       </c>
       <c r="J154" t="s">
         <v>1375</v>
@@ -21018,13 +21018,13 @@
         <v>3.75</v>
       </c>
       <c r="G155">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H155">
         <v>0.84455000000000002</v>
       </c>
       <c r="I155">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J155" t="s">
         <v>308</v>
@@ -21047,13 +21047,13 @@
         <v>3.75</v>
       </c>
       <c r="G156">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="H156">
         <v>0.84455000000000002</v>
       </c>
       <c r="I156">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J156" t="s">
         <v>309</v>
@@ -21076,13 +21076,13 @@
         <v>3.75</v>
       </c>
       <c r="G157">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="H157">
         <v>0.84455000000000002</v>
       </c>
       <c r="I157">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="J157" t="s">
         <v>310</v>
@@ -21105,13 +21105,13 @@
         <v>3.75</v>
       </c>
       <c r="G158">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H158">
         <v>0.84455000000000002</v>
       </c>
       <c r="I158">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J158" t="s">
         <v>311</v>
@@ -21134,13 +21134,13 @@
         <v>3.75</v>
       </c>
       <c r="G159">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H159">
         <v>0.84455000000000002</v>
       </c>
       <c r="I159">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J159" t="s">
         <v>313</v>
@@ -21163,13 +21163,13 @@
         <v>3.75</v>
       </c>
       <c r="G160">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H160">
         <v>0.84455000000000002</v>
       </c>
       <c r="I160">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J160" t="s">
         <v>314</v>
@@ -21192,13 +21192,13 @@
         <v>3.75</v>
       </c>
       <c r="G161">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H161">
         <v>0.84455000000000002</v>
       </c>
       <c r="I161">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J161" t="s">
         <v>315</v>
@@ -21221,13 +21221,13 @@
         <v>3.75</v>
       </c>
       <c r="G162">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H162">
         <v>0.84455000000000002</v>
       </c>
       <c r="I162">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J162" t="s">
         <v>316</v>
@@ -21250,13 +21250,13 @@
         <v>3.75</v>
       </c>
       <c r="G163">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="H163">
         <v>0.84455000000000002</v>
       </c>
       <c r="I163">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="J163" t="s">
         <v>317</v>
@@ -21279,13 +21279,13 @@
         <v>3.75</v>
       </c>
       <c r="G164">
-        <v>0.19162500000000002</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="H164">
         <v>0.84455000000000002</v>
       </c>
       <c r="I164">
-        <v>0.21900000000000003</v>
+        <v>0.183</v>
       </c>
       <c r="J164" t="s">
         <v>1376</v>
@@ -21308,13 +21308,13 @@
         <v>3.75</v>
       </c>
       <c r="G165">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H165">
         <v>0.84455000000000002</v>
       </c>
       <c r="I165">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J165" t="s">
         <v>1377</v>
@@ -21337,13 +21337,13 @@
         <v>3.75</v>
       </c>
       <c r="G166">
-        <v>0.20439999999999997</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="H166">
         <v>0.84455000000000002</v>
       </c>
       <c r="I166">
-        <v>0.23359999999999997</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="J166" t="s">
         <v>1378</v>
@@ -21366,13 +21366,13 @@
         <v>3.75</v>
       </c>
       <c r="G167">
-        <v>0.19162499999999999</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="H167">
         <v>0.84455000000000002</v>
       </c>
       <c r="I167">
-        <v>0.21899999999999997</v>
+        <v>0.183</v>
       </c>
       <c r="J167" t="s">
         <v>1379</v>
@@ -21395,13 +21395,13 @@
         <v>3.75</v>
       </c>
       <c r="G168">
-        <v>0.19162500000000002</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="H168">
         <v>0.84455000000000002</v>
       </c>
       <c r="I168">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="J168" t="s">
         <v>1380</v>
@@ -21424,13 +21424,13 @@
         <v>3.75</v>
       </c>
       <c r="G169">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H169">
         <v>0.84455000000000002</v>
       </c>
       <c r="I169">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J169" t="s">
         <v>1381</v>
@@ -21453,13 +21453,13 @@
         <v>3.75</v>
       </c>
       <c r="G170">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="H170">
         <v>0.84455000000000002</v>
       </c>
       <c r="I170">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="J170" t="s">
         <v>1382</v>
@@ -21471,7 +21471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC38696-B470-4C52-B6A7-4627145540C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9C80E8-FBCE-4D37-8323-7710EE334C22}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21903,13 +21903,13 @@
         <v>0.88</v>
       </c>
       <c r="E33">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F33">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="G33">
-        <v>29.2</v>
+        <v>34.9</v>
       </c>
       <c r="H33">
         <v>16.7</v>
@@ -21929,13 +21929,13 @@
         <v>0.45</v>
       </c>
       <c r="E34">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="F34">
-        <v>82.5</v>
+        <v>98.8</v>
       </c>
       <c r="G34">
-        <v>82</v>
+        <v>98.2</v>
       </c>
       <c r="H34">
         <v>74.2</v>
@@ -21955,13 +21955,13 @@
         <v>0.5</v>
       </c>
       <c r="E35">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="F35">
-        <v>717.7</v>
+        <v>858.8</v>
       </c>
       <c r="G35">
-        <v>537.29999999999995</v>
+        <v>643</v>
       </c>
       <c r="H35">
         <v>448.1</v>
@@ -22044,13 +22044,13 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="E39">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="F39">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="G39">
-        <v>33.5</v>
+        <v>39.1</v>
       </c>
       <c r="H39">
         <v>69.400000000000006</v>
@@ -22112,7 +22112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71A9878-1353-4F0C-B671-A484ED92A8C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B42030-DDCC-4779-AE93-9058097563EF}">
   <dimension ref="A1:Y508"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25510,7 +25510,7 @@
         <v>9.6</v>
       </c>
       <c r="P78">
-        <v>0.21899999999999997</v>
+        <v>0.183</v>
       </c>
       <c r="R78">
         <v>38</v>
@@ -25575,7 +25575,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P79">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R79">
         <v>38</v>
@@ -25640,7 +25640,7 @@
         <v>9.6</v>
       </c>
       <c r="P80">
-        <v>0.219</v>
+        <v>0.18300000000000002</v>
       </c>
       <c r="R80">
         <v>38</v>
@@ -25705,7 +25705,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P81">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R81">
         <v>38</v>
@@ -25770,7 +25770,7 @@
         <v>9.6</v>
       </c>
       <c r="P82">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R82">
         <v>38</v>
@@ -25835,7 +25835,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P83">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R83">
         <v>38</v>
@@ -25900,7 +25900,7 @@
         <v>9.6</v>
       </c>
       <c r="P84">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R84">
         <v>38</v>
@@ -25965,7 +25965,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P85">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R85">
         <v>38</v>
@@ -26030,7 +26030,7 @@
         <v>9.6</v>
       </c>
       <c r="P86">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R86">
         <v>38</v>
@@ -26095,7 +26095,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P87">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R87">
         <v>38</v>
@@ -26160,7 +26160,7 @@
         <v>9.6</v>
       </c>
       <c r="P88">
-        <v>0.219</v>
+        <v>0.18300000000000002</v>
       </c>
       <c r="R88">
         <v>38</v>
@@ -26225,7 +26225,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P89">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R89">
         <v>38</v>
@@ -26290,7 +26290,7 @@
         <v>9.6</v>
       </c>
       <c r="P90">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R90">
         <v>38</v>
@@ -26355,7 +26355,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P91">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R91">
         <v>38</v>
@@ -26408,7 +26408,7 @@
         <v>1.9999999999997797E-3</v>
       </c>
       <c r="P92">
-        <v>0.24179790000000001</v>
+        <v>0.20205030000000002</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.45">
@@ -26455,7 +26455,7 @@
         <v>5.5</v>
       </c>
       <c r="P93">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R93">
         <v>42</v>
@@ -26526,7 +26526,7 @@
         <v>5.5</v>
       </c>
       <c r="P94">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R94">
         <v>42</v>
@@ -26597,7 +26597,7 @@
         <v>5.5</v>
       </c>
       <c r="P95">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R95">
         <v>42</v>
@@ -26668,7 +26668,7 @@
         <v>5.5</v>
       </c>
       <c r="P96">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R96">
         <v>42</v>
@@ -26742,7 +26742,7 @@
         <v>5</v>
       </c>
       <c r="P97">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R97">
         <v>42</v>
@@ -26816,7 +26816,7 @@
         <v>5</v>
       </c>
       <c r="P98">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R98">
         <v>42</v>
@@ -26890,7 +26890,7 @@
         <v>5</v>
       </c>
       <c r="P99">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R99">
         <v>42</v>
@@ -26964,7 +26964,7 @@
         <v>5</v>
       </c>
       <c r="P100">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R100">
         <v>42</v>
@@ -27035,7 +27035,7 @@
         <v>5</v>
       </c>
       <c r="P101">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R101">
         <v>42</v>
@@ -27106,7 +27106,7 @@
         <v>5</v>
       </c>
       <c r="P102">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R102">
         <v>42</v>
@@ -27177,7 +27177,7 @@
         <v>5</v>
       </c>
       <c r="P103">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R103">
         <v>42</v>
@@ -27248,7 +27248,7 @@
         <v>5</v>
       </c>
       <c r="P104">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R104">
         <v>42</v>
@@ -27319,7 +27319,7 @@
         <v>5</v>
       </c>
       <c r="P105">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R105">
         <v>42</v>
@@ -27390,7 +27390,7 @@
         <v>5</v>
       </c>
       <c r="P106">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R106">
         <v>42</v>
@@ -27461,7 +27461,7 @@
         <v>5.5</v>
       </c>
       <c r="P107">
-        <v>0.28835</v>
+        <v>0.24095</v>
       </c>
       <c r="R107">
         <v>48</v>
@@ -27532,7 +27532,7 @@
         <v>3</v>
       </c>
       <c r="P108">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R108">
         <v>55</v>
@@ -27603,7 +27603,7 @@
         <v>3</v>
       </c>
       <c r="P109">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R109">
         <v>55</v>
@@ -27674,7 +27674,7 @@
         <v>3</v>
       </c>
       <c r="P110">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R110">
         <v>55</v>
@@ -27745,7 +27745,7 @@
         <v>3</v>
       </c>
       <c r="P111">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R111">
         <v>55</v>
@@ -27816,7 +27816,7 @@
         <v>3</v>
       </c>
       <c r="P112">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R112">
         <v>55</v>
@@ -27887,7 +27887,7 @@
         <v>3</v>
       </c>
       <c r="P113">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R113">
         <v>55</v>
@@ -27958,7 +27958,7 @@
         <v>3</v>
       </c>
       <c r="P114">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="R114">
         <v>55</v>
@@ -28029,7 +28029,7 @@
         <v>3</v>
       </c>
       <c r="P115">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="R115">
         <v>55</v>
@@ -28100,7 +28100,7 @@
         <v>3</v>
       </c>
       <c r="P116">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R116">
         <v>55</v>
@@ -28171,7 +28171,7 @@
         <v>3</v>
       </c>
       <c r="P117">
-        <v>0.42339999999999989</v>
+        <v>0.3538</v>
       </c>
       <c r="R117">
         <v>55</v>
@@ -28242,7 +28242,7 @@
         <v>3</v>
       </c>
       <c r="P118">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R118">
         <v>55</v>
@@ -28313,7 +28313,7 @@
         <v>3</v>
       </c>
       <c r="P119">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R119">
         <v>55</v>
@@ -28384,7 +28384,7 @@
         <v>3</v>
       </c>
       <c r="P120">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R120">
         <v>55</v>
@@ -28455,7 +28455,7 @@
         <v>3</v>
       </c>
       <c r="P121">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R121">
         <v>55</v>
@@ -28526,7 +28526,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P122">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R122">
         <v>50</v>
@@ -28597,7 +28597,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P123">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R123">
         <v>50</v>
@@ -28668,7 +28668,7 @@
         <v>3</v>
       </c>
       <c r="P124">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R124">
         <v>55</v>
@@ -28739,7 +28739,7 @@
         <v>3</v>
       </c>
       <c r="P125">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R125">
         <v>55</v>
@@ -28810,7 +28810,7 @@
         <v>3</v>
       </c>
       <c r="P126">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R126">
         <v>55</v>
@@ -28881,7 +28881,7 @@
         <v>3</v>
       </c>
       <c r="P127">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R127">
         <v>55</v>
@@ -28952,7 +28952,7 @@
         <v>3</v>
       </c>
       <c r="P128">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="R128">
         <v>55</v>
@@ -29023,7 +29023,7 @@
         <v>3</v>
       </c>
       <c r="P129">
-        <v>0.32850000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="R129">
         <v>55</v>
@@ -29094,7 +29094,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="P130">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R130">
         <v>55</v>
@@ -29165,7 +29165,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P131">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R131">
         <v>50</v>
@@ -29236,7 +29236,7 @@
         <v>3</v>
       </c>
       <c r="P132">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999989</v>
       </c>
       <c r="R132">
         <v>55</v>
@@ -29307,7 +29307,7 @@
         <v>3</v>
       </c>
       <c r="P133">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="R133">
         <v>55</v>
@@ -29378,7 +29378,7 @@
         <v>3</v>
       </c>
       <c r="P134">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R134">
         <v>55</v>
@@ -29449,7 +29449,7 @@
         <v>3</v>
       </c>
       <c r="P135">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R135">
         <v>55</v>
@@ -29520,7 +29520,7 @@
         <v>3</v>
       </c>
       <c r="P136">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R136">
         <v>55</v>
@@ -29591,7 +29591,7 @@
         <v>3</v>
       </c>
       <c r="P137">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R137">
         <v>55</v>
@@ -29662,7 +29662,7 @@
         <v>3.0000000000000004</v>
       </c>
       <c r="P138">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="R138">
         <v>55</v>
@@ -29733,7 +29733,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="P139">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="R139">
         <v>55</v>
@@ -29804,7 +29804,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P140">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R140">
         <v>50</v>
@@ -29875,7 +29875,7 @@
         <v>3</v>
       </c>
       <c r="P141">
-        <v>0.39784999999999998</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R141">
         <v>55</v>
@@ -29946,7 +29946,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P142">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R142">
         <v>50</v>
@@ -30017,7 +30017,7 @@
         <v>3</v>
       </c>
       <c r="P143">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R143">
         <v>55</v>
@@ -30088,7 +30088,7 @@
         <v>3</v>
       </c>
       <c r="P144">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R144">
         <v>55</v>
@@ -30159,7 +30159,7 @@
         <v>3</v>
       </c>
       <c r="P145">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R145">
         <v>55</v>
@@ -30230,7 +30230,7 @@
         <v>3</v>
       </c>
       <c r="P146">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R146">
         <v>55</v>
@@ -30301,7 +30301,7 @@
         <v>3</v>
       </c>
       <c r="P147">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R147">
         <v>55</v>
@@ -30372,7 +30372,7 @@
         <v>3</v>
       </c>
       <c r="P148">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R148">
         <v>55</v>
@@ -30443,7 +30443,7 @@
         <v>3</v>
       </c>
       <c r="P149">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R149">
         <v>55</v>
@@ -30514,7 +30514,7 @@
         <v>3</v>
       </c>
       <c r="P150">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R150">
         <v>55</v>
@@ -30585,7 +30585,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P151">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R151">
         <v>50</v>
@@ -30656,7 +30656,7 @@
         <v>3.0000000000000004</v>
       </c>
       <c r="P152">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="R152">
         <v>55</v>
@@ -30727,7 +30727,7 @@
         <v>3</v>
       </c>
       <c r="P153">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R153">
         <v>55</v>
@@ -30798,7 +30798,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P154">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R154">
         <v>50</v>
@@ -30869,7 +30869,7 @@
         <v>3</v>
       </c>
       <c r="P155">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="R155">
         <v>55</v>
@@ -30940,7 +30940,7 @@
         <v>3</v>
       </c>
       <c r="P156">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R156">
         <v>55</v>
@@ -31011,7 +31011,7 @@
         <v>3</v>
       </c>
       <c r="P157">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R157">
         <v>55</v>
@@ -31082,7 +31082,7 @@
         <v>3</v>
       </c>
       <c r="P158">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R158">
         <v>55</v>
@@ -31153,7 +31153,7 @@
         <v>3</v>
       </c>
       <c r="P159">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R159">
         <v>55</v>
@@ -31224,7 +31224,7 @@
         <v>3</v>
       </c>
       <c r="P160">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R160">
         <v>55</v>
@@ -31295,7 +31295,7 @@
         <v>3</v>
       </c>
       <c r="P161">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R161">
         <v>55</v>
@@ -31366,7 +31366,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P162">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R162">
         <v>50</v>
@@ -31437,7 +31437,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P163">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R163">
         <v>50</v>
@@ -31508,7 +31508,7 @@
         <v>3</v>
       </c>
       <c r="P164">
-        <v>0.43799999999999994</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R164">
         <v>55</v>
@@ -31579,7 +31579,7 @@
         <v>3</v>
       </c>
       <c r="P165">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R165">
         <v>55</v>
@@ -31650,7 +31650,7 @@
         <v>3</v>
       </c>
       <c r="P166">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R166">
         <v>55</v>
@@ -31721,7 +31721,7 @@
         <v>3</v>
       </c>
       <c r="P167">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R167">
         <v>55</v>
@@ -31792,7 +31792,7 @@
         <v>3</v>
       </c>
       <c r="P168">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R168">
         <v>55</v>
@@ -31863,7 +31863,7 @@
         <v>3</v>
       </c>
       <c r="P169">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R169">
         <v>55</v>
@@ -31934,7 +31934,7 @@
         <v>3</v>
       </c>
       <c r="P170">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R170">
         <v>55</v>
@@ -32005,7 +32005,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P171">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R171">
         <v>55</v>
@@ -32076,7 +32076,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P172">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R172">
         <v>50</v>
@@ -32147,7 +32147,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P173">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R173">
         <v>50</v>
@@ -32218,7 +32218,7 @@
         <v>3</v>
       </c>
       <c r="P174">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R174">
         <v>55</v>
@@ -32289,7 +32289,7 @@
         <v>3</v>
       </c>
       <c r="P175">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R175">
         <v>55</v>
@@ -32360,7 +32360,7 @@
         <v>3</v>
       </c>
       <c r="P176">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R176">
         <v>55</v>
@@ -32431,7 +32431,7 @@
         <v>3</v>
       </c>
       <c r="P177">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R177">
         <v>55</v>
@@ -32502,7 +32502,7 @@
         <v>3</v>
       </c>
       <c r="P178">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="R178">
         <v>55</v>
@@ -32573,7 +32573,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P179">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R179">
         <v>50</v>
@@ -32644,7 +32644,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P180">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R180">
         <v>50</v>
@@ -32715,7 +32715,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P181">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R181">
         <v>50</v>
@@ -32786,7 +32786,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P182">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R182">
         <v>50</v>
@@ -32857,7 +32857,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P183">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R183">
         <v>50</v>
@@ -32928,7 +32928,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P184">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R184">
         <v>50</v>
@@ -32999,7 +32999,7 @@
         <v>2.9999999999999996</v>
       </c>
       <c r="P185">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="R185">
         <v>55</v>
@@ -33070,7 +33070,7 @@
         <v>3</v>
       </c>
       <c r="P186">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="R186">
         <v>55</v>
@@ -33141,7 +33141,7 @@
         <v>3</v>
       </c>
       <c r="P187">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R187">
         <v>55</v>
@@ -33206,7 +33206,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P188">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R188">
         <v>55</v>
@@ -33271,7 +33271,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P189">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R189">
         <v>50</v>
@@ -33336,7 +33336,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P190">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R190">
         <v>50</v>
@@ -33401,7 +33401,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P191">
-        <v>0.36500000000000005</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R191">
         <v>55</v>
@@ -33466,7 +33466,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P192">
-        <v>0.4088</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R192">
         <v>50</v>
@@ -33531,7 +33531,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P193">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R193">
         <v>50</v>
@@ -33596,7 +33596,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P194">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R194">
         <v>50</v>
@@ -33661,7 +33661,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P195">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R195">
         <v>55</v>
@@ -33726,7 +33726,7 @@
         <v>3.3</v>
       </c>
       <c r="P196">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R196">
         <v>50</v>
@@ -33791,7 +33791,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P197">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R197">
         <v>50</v>
@@ -33856,7 +33856,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P198">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="R198">
         <v>50</v>
@@ -33921,7 +33921,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P199">
-        <v>0.27739999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="R199">
         <v>50</v>
@@ -33986,7 +33986,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P200">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000007</v>
       </c>
       <c r="R200">
         <v>50</v>
@@ -34051,7 +34051,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P201">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R201">
         <v>50</v>
@@ -34116,7 +34116,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P202">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="R202">
         <v>50</v>
@@ -34181,7 +34181,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="P203">
-        <v>0.37960000000000005</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="R203">
         <v>50</v>
@@ -34246,7 +34246,7 @@
         <v>3.3000000000000007</v>
       </c>
       <c r="P204">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R204">
         <v>50</v>
@@ -34317,7 +34317,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P205">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R205">
         <v>35</v>
@@ -34388,7 +34388,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P206">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R206">
         <v>35</v>
@@ -34453,7 +34453,7 @@
         <v>4.8</v>
       </c>
       <c r="P207">
-        <v>0.18615000000000001</v>
+        <v>0.15554999999999999</v>
       </c>
       <c r="R207">
         <v>30</v>
@@ -34518,7 +34518,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P208">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R208">
         <v>30</v>
@@ -34583,7 +34583,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P209">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R209">
         <v>30</v>
@@ -34648,7 +34648,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P210">
-        <v>0.19345000000000001</v>
+        <v>0.16165000000000002</v>
       </c>
       <c r="R210">
         <v>30</v>
@@ -34713,7 +34713,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P211">
-        <v>0.21169999999999997</v>
+        <v>0.17689999999999997</v>
       </c>
       <c r="R211">
         <v>30</v>
@@ -34778,7 +34778,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P212">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R212">
         <v>35</v>
@@ -34843,7 +34843,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P213">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R213">
         <v>30</v>
@@ -34908,7 +34908,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="P214">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R214">
         <v>35</v>
@@ -34979,7 +34979,7 @@
         <v>6.5</v>
       </c>
       <c r="P215">
-        <v>0.26279999999999998</v>
+        <v>0.21960000000000002</v>
       </c>
       <c r="R215">
         <v>35</v>
@@ -35050,7 +35050,7 @@
         <v>6.5</v>
       </c>
       <c r="P216">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R216">
         <v>35</v>
@@ -35115,7 +35115,7 @@
         <v>7.15</v>
       </c>
       <c r="P217">
-        <v>0.25914999999999999</v>
+        <v>0.21654999999999999</v>
       </c>
       <c r="R217">
         <v>35</v>
@@ -35180,7 +35180,7 @@
         <v>7.15</v>
       </c>
       <c r="P218">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R218">
         <v>35</v>
@@ -35245,7 +35245,7 @@
         <v>7.15</v>
       </c>
       <c r="P219">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="R219">
         <v>35</v>
@@ -35316,7 +35316,7 @@
         <v>4.95</v>
       </c>
       <c r="P220">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R220">
         <v>40</v>
@@ -35387,7 +35387,7 @@
         <v>4.95</v>
       </c>
       <c r="P221">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R221">
         <v>40</v>
@@ -35458,7 +35458,7 @@
         <v>4.5</v>
       </c>
       <c r="P222">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R222">
         <v>40</v>
@@ -35529,7 +35529,7 @@
         <v>4.5</v>
       </c>
       <c r="P223">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R223">
         <v>40</v>
@@ -35600,7 +35600,7 @@
         <v>4.95</v>
       </c>
       <c r="P224">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R224">
         <v>40</v>
@@ -35671,7 +35671,7 @@
         <v>4.95</v>
       </c>
       <c r="P225">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R225">
         <v>40</v>
@@ -35742,7 +35742,7 @@
         <v>4.95</v>
       </c>
       <c r="P226">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R226">
         <v>40</v>
@@ -35813,7 +35813,7 @@
         <v>4.95</v>
       </c>
       <c r="P227">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R227">
         <v>40</v>
@@ -35884,7 +35884,7 @@
         <v>4.95</v>
       </c>
       <c r="P228">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R228">
         <v>40</v>
@@ -35955,7 +35955,7 @@
         <v>4.95</v>
       </c>
       <c r="P229">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R229">
         <v>40</v>
@@ -36020,7 +36020,7 @@
         <v>4.95</v>
       </c>
       <c r="P230">
-        <v>0.2482</v>
+        <v>0.20739999999999997</v>
       </c>
       <c r="R230">
         <v>35</v>
@@ -36085,7 +36085,7 @@
         <v>4.95</v>
       </c>
       <c r="P231">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R231">
         <v>35</v>
@@ -36150,7 +36150,7 @@
         <v>4.95</v>
       </c>
       <c r="P232">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R232">
         <v>35</v>
@@ -36215,7 +36215,7 @@
         <v>4.95</v>
       </c>
       <c r="P233">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R233">
         <v>40</v>
@@ -36280,7 +36280,7 @@
         <v>4.95</v>
       </c>
       <c r="P234">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R234">
         <v>35</v>
@@ -36345,7 +36345,7 @@
         <v>4.95</v>
       </c>
       <c r="P235">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R235">
         <v>40</v>
@@ -36410,7 +36410,7 @@
         <v>4.95</v>
       </c>
       <c r="P236">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R236">
         <v>35</v>
@@ -36475,7 +36475,7 @@
         <v>4.95</v>
       </c>
       <c r="P237">
-        <v>0.24089999999999998</v>
+        <v>0.20129999999999998</v>
       </c>
       <c r="R237">
         <v>40</v>
@@ -36540,7 +36540,7 @@
         <v>4.95</v>
       </c>
       <c r="P238">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R238">
         <v>35</v>
@@ -36605,7 +36605,7 @@
         <v>4.95</v>
       </c>
       <c r="P239">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R239">
         <v>35</v>
@@ -36670,7 +36670,7 @@
         <v>4.95</v>
       </c>
       <c r="P240">
-        <v>0.24819999999999998</v>
+        <v>0.2074</v>
       </c>
       <c r="R240">
         <v>35</v>
@@ -36735,7 +36735,7 @@
         <v>4.95</v>
       </c>
       <c r="P241">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R241">
         <v>35</v>
@@ -40036,7 +40036,7 @@
         <v>3.850000000000001</v>
       </c>
       <c r="P318">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="R318">
         <v>50</v>
@@ -40101,7 +40101,7 @@
         <v>4.95</v>
       </c>
       <c r="P319">
-        <v>0.17519999999999999</v>
+        <v>0.1464</v>
       </c>
       <c r="R319">
         <v>30</v>
@@ -40172,7 +40172,7 @@
         <v>5</v>
       </c>
       <c r="P320">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R320">
         <v>40</v>
@@ -40243,7 +40243,7 @@
         <v>5</v>
       </c>
       <c r="P321">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R321">
         <v>40</v>
@@ -40314,7 +40314,7 @@
         <v>5</v>
       </c>
       <c r="P322">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="R322">
         <v>40</v>
@@ -40385,7 +40385,7 @@
         <v>5</v>
       </c>
       <c r="P323">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R323">
         <v>40</v>
@@ -40456,7 +40456,7 @@
         <v>5</v>
       </c>
       <c r="P324">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R324">
         <v>40</v>
@@ -40527,7 +40527,7 @@
         <v>5</v>
       </c>
       <c r="P325">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R325">
         <v>40</v>
@@ -40598,7 +40598,7 @@
         <v>5</v>
       </c>
       <c r="P326">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R326">
         <v>40</v>
@@ -40669,7 +40669,7 @@
         <v>5</v>
       </c>
       <c r="P327">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R327">
         <v>40</v>
@@ -40740,7 +40740,7 @@
         <v>5</v>
       </c>
       <c r="P328">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="R328">
         <v>40</v>
@@ -40805,7 +40805,7 @@
         <v>5.5</v>
       </c>
       <c r="P329">
-        <v>0.21900000000000003</v>
+        <v>0.183</v>
       </c>
       <c r="R329">
         <v>40</v>
@@ -40870,7 +40870,7 @@
         <v>5.5</v>
       </c>
       <c r="P330">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R330">
         <v>40</v>
@@ -40935,7 +40935,7 @@
         <v>5.5</v>
       </c>
       <c r="P331">
-        <v>0.23359999999999997</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="R331">
         <v>40</v>
@@ -41000,7 +41000,7 @@
         <v>5.5</v>
       </c>
       <c r="P332">
-        <v>0.21899999999999997</v>
+        <v>0.183</v>
       </c>
       <c r="R332">
         <v>40</v>
@@ -41065,7 +41065,7 @@
         <v>5.5</v>
       </c>
       <c r="P333">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="R333">
         <v>35</v>
@@ -41130,7 +41130,7 @@
         <v>5.5</v>
       </c>
       <c r="P334">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R334">
         <v>35</v>
@@ -41195,7 +41195,7 @@
         <v>5.5</v>
       </c>
       <c r="P335">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="R335">
         <v>40</v>
